--- a/data/花店价格/抖音小时达/抖音价格0417.xlsx
+++ b/data/花店价格/抖音小时达/抖音价格0417.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="157">
   <si>
     <t>本页为说明，请看下方，修改第二个sheet页</t>
   </si>
@@ -89,21 +89,36 @@
     <t>3724690734171947098</t>
   </si>
   <si>
+    <t>119.0</t>
+  </si>
+  <si>
     <t>3724693409936572580</t>
   </si>
   <si>
+    <t>39.0</t>
+  </si>
+  <si>
     <t>3724693216612712597</t>
   </si>
   <si>
     <t>3724691062812442971</t>
   </si>
   <si>
+    <t>49.0</t>
+  </si>
+  <si>
     <t>3724689142802677935</t>
   </si>
   <si>
+    <t>79.0</t>
+  </si>
+  <si>
     <t>3724689454330413314</t>
   </si>
   <si>
+    <t>59.0</t>
+  </si>
+  <si>
     <t>3724484693954003439</t>
   </si>
   <si>
@@ -116,24 +131,45 @@
     <t>3724691801412600044</t>
   </si>
   <si>
+    <t>99.0</t>
+  </si>
+  <si>
     <t>3724693345486897484</t>
   </si>
   <si>
+    <t>288.0</t>
+  </si>
+  <si>
     <t>3728355440728342625</t>
   </si>
   <si>
+    <t>168.0</t>
+  </si>
+  <si>
     <t>3725022187518820728</t>
   </si>
   <si>
+    <t>328.0</t>
+  </si>
+  <si>
     <t>3724694176688898329</t>
   </si>
   <si>
+    <t>988.0</t>
+  </si>
+  <si>
     <t>3724692759148364063</t>
   </si>
   <si>
+    <t>109.0</t>
+  </si>
+  <si>
     <t>3725206428714139885</t>
   </si>
   <si>
+    <t>149.0</t>
+  </si>
+  <si>
     <t>3725026248368456041</t>
   </si>
   <si>
@@ -149,6 +185,9 @@
     <t>3725021693555638362</t>
   </si>
   <si>
+    <t>158.0</t>
+  </si>
+  <si>
     <t>3724694887388545058</t>
   </si>
   <si>
@@ -158,6 +197,9 @@
     <t>3726691291191443814</t>
   </si>
   <si>
+    <t>89.0</t>
+  </si>
+  <si>
     <t>3727236335417819484</t>
   </si>
   <si>
@@ -165,6 +207,9 @@
   </si>
   <si>
     <t>3724695153626185985</t>
+  </si>
+  <si>
+    <t>358.0</t>
   </si>
   <si>
     <t>3728355659712954580</t>
@@ -497,7 +542,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,6 +554,13 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -965,148 +1017,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1114,7 +1166,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1528,311 +1579,311 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2">
-        <v>119</v>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
+      <c r="A5" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2">
-        <v>39</v>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
+      <c r="A6" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2">
-        <v>39</v>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>20</v>
+      <c r="A7" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2">
-        <v>49</v>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>21</v>
+      <c r="A8" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2">
-        <v>79</v>
+      <c r="C8" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
-        <v>22</v>
+      <c r="A9" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2">
-        <v>59</v>
+      <c r="C9" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>23</v>
+      <c r="A10" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2">
-        <v>49</v>
+      <c r="C10" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
-        <v>24</v>
+      <c r="A11" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="2">
-        <v>39</v>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
-        <v>25</v>
+      <c r="A12" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2">
-        <v>39</v>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="3" t="s">
-        <v>26</v>
+      <c r="A13" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="2">
-        <v>99</v>
+      <c r="C13" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>27</v>
+      <c r="A14" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="2">
-        <v>288</v>
+      <c r="C14" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>28</v>
+      <c r="A15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2">
-        <v>168</v>
+      <c r="C15" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
-        <v>29</v>
+      <c r="A16" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2">
-        <v>328</v>
+      <c r="C16" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>30</v>
+      <c r="A17" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="2">
-        <v>988</v>
+      <c r="C17" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>31</v>
+      <c r="A18" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="2">
-        <v>109</v>
+      <c r="C18" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
-        <v>32</v>
+      <c r="A19" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="2">
-        <v>149</v>
+      <c r="C19" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="3" t="s">
-        <v>33</v>
+      <c r="A20" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="2">
-        <v>49</v>
+      <c r="C20" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
-        <v>34</v>
+      <c r="A21" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="2">
-        <v>168</v>
+      <c r="C21" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>35</v>
+      <c r="A22" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="2">
-        <v>149</v>
+      <c r="C22" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>36</v>
+      <c r="A23" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="2">
-        <v>79</v>
+      <c r="C23" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>37</v>
+      <c r="A24" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="2">
-        <v>158</v>
+      <c r="C24" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>38</v>
+      <c r="A25" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="2">
-        <v>168</v>
+      <c r="C25" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>39</v>
+      <c r="A26" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="2">
-        <v>168</v>
+      <c r="C26" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>40</v>
+      <c r="A27" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="2">
-        <v>89</v>
+      <c r="C27" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>41</v>
+      <c r="A28" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="2">
-        <v>99</v>
+      <c r="C28" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>42</v>
+      <c r="A29" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="2">
-        <v>49</v>
+      <c r="C29" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>43</v>
+      <c r="A30" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="2">
-        <v>358</v>
+      <c r="C30" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>44</v>
+      <c r="A31" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="2">
-        <v>109</v>
+      <c r="C31" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1852,13 +1903,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1866,340 +1917,340 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2221,25 +2272,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="F1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2247,712 +2298,712 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" t="s">
         <v>106</v>
       </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
-      </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G13" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="F14" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" t="s">
         <v>114</v>
       </c>
-      <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" t="s">
-        <v>99</v>
-      </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G18" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="F20" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="G20" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G22" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G24" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F27" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G27" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G28" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G29" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="F30" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G30" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G31" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="E32" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="G32" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data/花店价格/抖音小时达/抖音价格0417.xlsx
+++ b/data/花店价格/抖音小时达/抖音价格0417.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="156">
   <si>
     <t>本页为说明，请看下方，修改第二个sheet页</t>
   </si>
@@ -95,7 +95,7 @@
     <t>3724693409936572580</t>
   </si>
   <si>
-    <t>39.0</t>
+    <t>59.0</t>
   </si>
   <si>
     <t>3724693216612712597</t>
@@ -104,24 +104,21 @@
     <t>3724691062812442971</t>
   </si>
   <si>
+    <t>3724689142802677935</t>
+  </si>
+  <si>
+    <t>79.0</t>
+  </si>
+  <si>
+    <t>3724689454330413314</t>
+  </si>
+  <si>
+    <t>3724484693954003439</t>
+  </si>
+  <si>
     <t>49.0</t>
   </si>
   <si>
-    <t>3724689142802677935</t>
-  </si>
-  <si>
-    <t>79.0</t>
-  </si>
-  <si>
-    <t>3724689454330413314</t>
-  </si>
-  <si>
-    <t>59.0</t>
-  </si>
-  <si>
-    <t>3724484693954003439</t>
-  </si>
-  <si>
     <t>3724687985493541261</t>
   </si>
   <si>
@@ -131,43 +128,43 @@
     <t>3724691801412600044</t>
   </si>
   <si>
+    <t>109.0</t>
+  </si>
+  <si>
+    <t>3724693345486897484</t>
+  </si>
+  <si>
+    <t>368.0</t>
+  </si>
+  <si>
+    <t>3728355440728342625</t>
+  </si>
+  <si>
+    <t>228.0</t>
+  </si>
+  <si>
+    <t>3725022187518820728</t>
+  </si>
+  <si>
+    <t>498.0</t>
+  </si>
+  <si>
+    <t>3724694176688898329</t>
+  </si>
+  <si>
+    <t>1988.0</t>
+  </si>
+  <si>
+    <t>3724692759148364063</t>
+  </si>
+  <si>
     <t>99.0</t>
   </si>
   <si>
-    <t>3724693345486897484</t>
-  </si>
-  <si>
-    <t>288.0</t>
-  </si>
-  <si>
-    <t>3728355440728342625</t>
-  </si>
-  <si>
-    <t>168.0</t>
-  </si>
-  <si>
-    <t>3725022187518820728</t>
-  </si>
-  <si>
-    <t>328.0</t>
-  </si>
-  <si>
-    <t>3724694176688898329</t>
-  </si>
-  <si>
-    <t>988.0</t>
-  </si>
-  <si>
-    <t>3724692759148364063</t>
-  </si>
-  <si>
-    <t>109.0</t>
-  </si>
-  <si>
     <t>3725206428714139885</t>
   </si>
   <si>
-    <t>149.0</t>
+    <t>188.0</t>
   </si>
   <si>
     <t>3725026248368456041</t>
@@ -176,6 +173,9 @@
     <t>3724694567522533554</t>
   </si>
   <si>
+    <t>198.0</t>
+  </si>
+  <si>
     <t>3725206604883297067</t>
   </si>
   <si>
@@ -185,9 +185,6 @@
     <t>3725021693555638362</t>
   </si>
   <si>
-    <t>158.0</t>
-  </si>
-  <si>
     <t>3724694887388545058</t>
   </si>
   <si>
@@ -209,7 +206,7 @@
     <t>3724695153626185985</t>
   </si>
   <si>
-    <t>358.0</t>
+    <t>598.0</t>
   </si>
   <si>
     <t>3728355659712954580</t>
@@ -1619,45 +1616,45 @@
         <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -1668,7 +1665,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
@@ -1679,101 +1676,101 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1784,7 +1781,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1795,7 +1792,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1806,84 +1803,84 @@
         <v>15</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1903,13 +1900,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>61</v>
-      </c>
-      <c r="C1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1917,10 +1914,10 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1928,10 +1925,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1939,10 +1936,10 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1950,186 +1947,186 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
         <v>73</v>
       </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s">
         <v>78</v>
       </c>
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -2137,10 +2134,10 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2148,10 +2145,10 @@
         <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2159,98 +2156,98 @@
         <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
         <v>93</v>
       </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2272,25 +2269,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" t="s">
         <v>61</v>
-      </c>
-      <c r="C1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2298,22 +2295,22 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
         <v>101</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>102</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>103</v>
       </c>
-      <c r="F2" t="s">
-        <v>104</v>
-      </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2321,22 +2318,22 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" t="s">
         <v>105</v>
       </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" t="s">
-        <v>106</v>
-      </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2344,22 +2341,22 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2367,390 +2364,390 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" t="s">
         <v>108</v>
       </c>
-      <c r="D5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F5" t="s">
-        <v>109</v>
-      </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
         <v>110</v>
       </c>
-      <c r="D6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" t="s">
-        <v>111</v>
-      </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" t="s">
         <v>112</v>
       </c>
-      <c r="D7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>113</v>
       </c>
-      <c r="F7" t="s">
-        <v>114</v>
-      </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
         <v>116</v>
       </c>
-      <c r="D9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>117</v>
       </c>
-      <c r="F9" t="s">
-        <v>118</v>
-      </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" t="s">
         <v>120</v>
       </c>
-      <c r="C11" t="s">
-        <v>121</v>
-      </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" t="s">
         <v>102</v>
       </c>
-      <c r="E12" t="s">
-        <v>103</v>
-      </c>
       <c r="F12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
         <v>123</v>
       </c>
-      <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
-        <v>124</v>
-      </c>
       <c r="F13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" t="s">
         <v>125</v>
       </c>
-      <c r="D14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" t="s">
-        <v>126</v>
-      </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s">
         <v>78</v>
       </c>
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
       <c r="C15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" t="s">
         <v>127</v>
       </c>
-      <c r="D15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" t="s">
-        <v>128</v>
-      </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" t="s">
         <v>130</v>
       </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>131</v>
-      </c>
       <c r="F17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D18" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" t="s">
         <v>102</v>
       </c>
-      <c r="E18" t="s">
-        <v>103</v>
-      </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" t="s">
         <v>133</v>
       </c>
-      <c r="D19" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" t="s">
-        <v>134</v>
-      </c>
       <c r="F19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2758,22 +2755,22 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2781,22 +2778,22 @@
         <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" t="s">
         <v>138</v>
       </c>
-      <c r="D23" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" t="s">
-        <v>139</v>
-      </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2804,206 +2801,206 @@
         <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" t="s">
         <v>140</v>
       </c>
-      <c r="D24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" t="s">
-        <v>141</v>
-      </c>
       <c r="F24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" t="s">
         <v>143</v>
       </c>
-      <c r="D26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" t="s">
-        <v>144</v>
-      </c>
       <c r="F26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" t="s">
         <v>145</v>
       </c>
-      <c r="D27" t="s">
-        <v>102</v>
-      </c>
-      <c r="E27" t="s">
-        <v>146</v>
-      </c>
       <c r="F27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" t="s">
         <v>102</v>
       </c>
-      <c r="E28" t="s">
-        <v>103</v>
-      </c>
       <c r="F28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" t="s">
         <v>148</v>
       </c>
-      <c r="D29" t="s">
-        <v>102</v>
-      </c>
-      <c r="E29" t="s">
-        <v>149</v>
-      </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
         <v>93</v>
       </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
       <c r="C30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" t="s">
         <v>150</v>
       </c>
-      <c r="D30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>151</v>
       </c>
-      <c r="F30" t="s">
-        <v>152</v>
-      </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" t="s">
         <v>153</v>
       </c>
-      <c r="D31" t="s">
-        <v>102</v>
-      </c>
-      <c r="E31" t="s">
-        <v>154</v>
-      </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" t="s">
         <v>155</v>
       </c>
-      <c r="D32" t="s">
-        <v>102</v>
-      </c>
-      <c r="E32" t="s">
-        <v>156</v>
-      </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/data/花店价格/抖音小时达/抖音价格0417.xlsx
+++ b/data/花店价格/抖音小时达/抖音价格0417.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="142">
   <si>
     <t>本页为说明，请看下方，修改第二个sheet页</t>
   </si>
@@ -89,15 +89,9 @@
     <t>3724690734171947098</t>
   </si>
   <si>
-    <t>119.0</t>
-  </si>
-  <si>
     <t>3724693409936572580</t>
   </si>
   <si>
-    <t>59.0</t>
-  </si>
-  <si>
     <t>3724693216612712597</t>
   </si>
   <si>
@@ -107,75 +101,48 @@
     <t>3724689142802677935</t>
   </si>
   <si>
-    <t>79.0</t>
-  </si>
-  <si>
     <t>3724689454330413314</t>
   </si>
   <si>
     <t>3724484693954003439</t>
   </si>
   <si>
-    <t>49.0</t>
-  </si>
-  <si>
     <t>3724687985493541261</t>
   </si>
   <si>
     <t>3724634805166539058</t>
   </si>
   <si>
+    <t>3724692772133929079</t>
+  </si>
+  <si>
     <t>3724691801412600044</t>
   </si>
   <si>
-    <t>109.0</t>
-  </si>
-  <si>
     <t>3724693345486897484</t>
   </si>
   <si>
-    <t>368.0</t>
-  </si>
-  <si>
     <t>3728355440728342625</t>
   </si>
   <si>
-    <t>228.0</t>
-  </si>
-  <si>
     <t>3725022187518820728</t>
   </si>
   <si>
-    <t>498.0</t>
-  </si>
-  <si>
     <t>3724694176688898329</t>
   </si>
   <si>
-    <t>1988.0</t>
-  </si>
-  <si>
     <t>3724692759148364063</t>
   </si>
   <si>
-    <t>99.0</t>
-  </si>
-  <si>
     <t>3725206428714139885</t>
   </si>
   <si>
-    <t>188.0</t>
-  </si>
-  <si>
     <t>3725026248368456041</t>
   </si>
   <si>
     <t>3724694567522533554</t>
   </si>
   <si>
-    <t>198.0</t>
-  </si>
-  <si>
     <t>3725206604883297067</t>
   </si>
   <si>
@@ -194,9 +161,6 @@
     <t>3726691291191443814</t>
   </si>
   <si>
-    <t>89.0</t>
-  </si>
-  <si>
     <t>3727236335417819484</t>
   </si>
   <si>
@@ -206,9 +170,6 @@
     <t>3724695153626185985</t>
   </si>
   <si>
-    <t>598.0</t>
-  </si>
-  <si>
     <t>3728355659712954580</t>
   </si>
   <si>
@@ -249,9 +210,6 @@
   </si>
   <si>
     <t>【热可可】11朵卡布奇诺玫瑰巧克力泡泡混搭韩式花束ins风</t>
-  </si>
-  <si>
-    <t>3724692772133929079</t>
   </si>
   <si>
     <t>【午后红茶】【送礼物袋】11朵粉雪山玫瑰混搭折射泡泡生日鲜花礼物</t>
@@ -539,7 +497,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,13 +509,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1014,148 +965,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1534,7 +1485,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
@@ -1582,305 +1533,316 @@
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
+      <c r="C4" s="2">
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
+      <c r="C5" s="2">
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
+      <c r="C6" s="2">
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
+      <c r="C7" s="2">
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>24</v>
+      <c r="C8" s="2">
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>24</v>
+      <c r="C9" s="2">
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>27</v>
+      <c r="C10" s="2">
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>20</v>
+      <c r="C11" s="2">
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>20</v>
+      <c r="C12" s="2">
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>31</v>
+      <c r="C13" s="2">
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>33</v>
+      <c r="C14" s="2">
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>35</v>
+      <c r="C15" s="2">
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>37</v>
+      <c r="C16" s="2">
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>39</v>
+      <c r="C17" s="2">
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>41</v>
+      <c r="C18" s="2">
+        <v>1288</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>43</v>
+      <c r="C19" s="2">
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>20</v>
+      <c r="C20" s="2">
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>46</v>
+      <c r="C21" s="2">
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>43</v>
+      <c r="C22" s="2">
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>31</v>
+      <c r="C23" s="2">
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>46</v>
+      <c r="C24" s="2">
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>43</v>
+      <c r="C25" s="2">
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>43</v>
+      <c r="C26" s="2">
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>53</v>
+      <c r="C27" s="2">
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>31</v>
+      <c r="C28" s="2">
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>20</v>
+      <c r="C29" s="2">
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>57</v>
+      <c r="C30" s="2">
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>18</v>
+      <c r="C31" s="2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1900,13 +1862,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1914,340 +1876,340 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2269,25 +2231,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F1" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2295,712 +2257,712 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="F13" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F18" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="F21" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F22" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F23" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F24" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="F25" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" t="s">
         <v>89</v>
       </c>
-      <c r="C26" t="s">
-        <v>142</v>
-      </c>
-      <c r="D26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" t="s">
-        <v>143</v>
-      </c>
-      <c r="F26" t="s">
-        <v>103</v>
-      </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="F27" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G30" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="F31" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G31" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="F32" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/花店价格/抖音小时达/抖音价格0417.xlsx
+++ b/data/花店价格/抖音小时达/抖音价格0417.xlsx
@@ -497,7 +497,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,6 +509,13 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -965,148 +972,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1534,7 +1541,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="2">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1644,7 +1651,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="2">
-        <v>88</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1666,7 +1673,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="2">
-        <v>188</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1677,7 +1684,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="2">
-        <v>268</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1699,7 +1706,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="2">
-        <v>88</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1710,7 +1717,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="2">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1732,7 +1739,7 @@
         <v>15</v>
       </c>
       <c r="C22" s="2">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1743,7 +1750,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1754,7 +1761,7 @@
         <v>15</v>
       </c>
       <c r="C24" s="2">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1765,7 +1772,7 @@
         <v>15</v>
       </c>
       <c r="C25" s="2">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1776,7 +1783,7 @@
         <v>15</v>
       </c>
       <c r="C26" s="2">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1787,7 +1794,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="2">
-        <v>168</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1809,7 +1816,7 @@
         <v>15</v>
       </c>
       <c r="C29" s="2">
-        <v>88</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1831,7 +1838,7 @@
         <v>15</v>
       </c>
       <c r="C31" s="2">
-        <v>388</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1842,7 +1849,7 @@
         <v>15</v>
       </c>
       <c r="C32" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
